--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -983,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1160,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1214,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1291,7 +1291,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3162,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3216,7 +3216,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3387,22 +3387,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.2</v>
+      </c>
       <c r="I3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3540,7 +3543,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3629,22 +3632,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920084</v>
+        <v>19330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3661,10 +3664,10 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3681,35 +3684,35 @@
         <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920088</v>
+        <v>19330051920090</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920090</v>
+        <v>19330051920089</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
@@ -3718,7 +3721,7 @@
         <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -3729,96 +3732,96 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920090</v>
+        <v>19330051920092</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920089</v>
+        <v>19330051920092</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920089</v>
+        <v>19330051920093</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -3829,16 +3832,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -3861,164 +3864,164 @@
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920094</v>
+        <v>19330051920095</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920094</v>
+        <v>19330051920095</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920094</v>
+        <v>19330051920095</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920095</v>
+        <v>19330051920097</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -4029,416 +4032,416 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920095</v>
+        <v>19330051920097</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
         <v>69</v>
       </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920097</v>
+        <v>19330051920098</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920097</v>
+        <v>19330051920099</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920098</v>
+        <v>19330051920099</v>
       </c>
       <c r="B30" t="s">
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920098</v>
+        <v>19330051920099</v>
       </c>
       <c r="B31" t="s">
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920098</v>
+        <v>19330051920100</v>
       </c>
       <c r="B32" t="s">
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920099</v>
+        <v>19330051920100</v>
       </c>
       <c r="B33" t="s">
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920099</v>
+        <v>19330051920101</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920099</v>
+        <v>19330051920101</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920100</v>
+        <v>19330051920101</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920100</v>
+        <v>19330051920102</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920101</v>
+        <v>19330051920102</v>
       </c>
       <c r="B38" t="s">
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920101</v>
+        <v>19330051920105</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920101</v>
+        <v>19330051920105</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920102</v>
+        <v>19330051920105</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920102</v>
+        <v>19330051920103</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920105</v>
+        <v>19330051920103</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920105</v>
+        <v>19330051920106</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920105</v>
+        <v>19330051920106</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -4449,16 +4452,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>19330051920103</v>
+        <v>19330051920107</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E46" t="s">
         <v>6</v>
@@ -4469,216 +4472,216 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>19330051920103</v>
+        <v>19330051920109</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>19330051920106</v>
+        <v>19330051920109</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>19330051920106</v>
+        <v>19330051920110</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>19330051920107</v>
+        <v>19330051920110</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>19330051920107</v>
+        <v>19330051920112</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
         <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>19330051920109</v>
+        <v>19330051920112</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>19330051920109</v>
+        <v>19330051920001</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>19330051920110</v>
+        <v>19330051920001</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>19330051920110</v>
+        <v>19330051920115</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>19330051920112</v>
+        <v>19330051920115</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>19330051920112</v>
+        <v>19330051920115</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -4689,16 +4692,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>19330051920001</v>
+        <v>19330051920116</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
@@ -4709,16 +4712,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>19330051920001</v>
+        <v>19330051920116</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -4729,16 +4732,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>19330051920115</v>
+        <v>19330051920117</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
@@ -4749,176 +4752,176 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>19330051920115</v>
+        <v>19330051920117</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="E61" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>19330051920115</v>
+        <v>19330051920118</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
         <v>74</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>19330051920116</v>
+        <v>19330051920118</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D63" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>19330051920116</v>
+        <v>19330051920119</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>19330051920117</v>
+        <v>19330051920119</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>19330051920117</v>
+        <v>19330051920120</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>19330051920118</v>
+        <v>19330051920120</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>19330051920118</v>
+        <v>19330051920121</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>19330051920119</v>
+        <v>19330051920122</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
@@ -4929,141 +4932,21 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>19330051920119</v>
+        <v>19330051920122</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920120</v>
-      </c>
-      <c r="B71" t="s">
-        <v>86</v>
-      </c>
-      <c r="C71" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" t="s">
-        <v>134</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920120</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" t="s">
-        <v>134</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920121</v>
-      </c>
-      <c r="B73" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" t="s">
-        <v>135</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920121</v>
-      </c>
-      <c r="B74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>135</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920122</v>
-      </c>
-      <c r="B75" t="s">
-        <v>88</v>
-      </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920122</v>
-      </c>
-      <c r="B76" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="s">
-        <v>136</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5151,16 +5034,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5168,16 +5051,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5185,16 +5068,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920098</v>
+        <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5202,16 +5085,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920099</v>
+        <v>19330051920101</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5219,16 +5102,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920101</v>
+        <v>19330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5236,16 +5119,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920105</v>
+        <v>19330051920115</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5253,33 +5136,33 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920115</v>
+        <v>19330051920085</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5287,16 +5170,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920084</v>
+        <v>19330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5304,16 +5187,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920090</v>
+        <v>19330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5321,16 +5204,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920089</v>
+        <v>19330051920102</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -5338,16 +5221,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920097</v>
+        <v>19330051920103</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -5355,16 +5238,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920100</v>
+        <v>19330051920106</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -5372,16 +5255,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920102</v>
+        <v>19330051920109</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -5389,16 +5272,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920103</v>
+        <v>19330051920110</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -5406,16 +5289,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920106</v>
+        <v>19330051920112</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -5423,16 +5306,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920107</v>
+        <v>19330051920001</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -5440,16 +5323,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920109</v>
+        <v>19330051920116</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -5457,16 +5340,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920110</v>
+        <v>19330051920117</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -5474,16 +5357,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920112</v>
+        <v>19330051920118</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -5491,16 +5374,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920001</v>
+        <v>19330051920119</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -5508,16 +5391,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920116</v>
+        <v>19330051920120</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -5525,16 +5408,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920117</v>
+        <v>19330051920122</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -5542,87 +5425,87 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920118</v>
+        <v>19330051920084</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920119</v>
+        <v>19330051920090</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920120</v>
+        <v>19330051920089</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920121</v>
+        <v>19330051920107</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920122</v>
+        <v>19330051920121</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5632,7 +5515,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5710,16 +5593,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920084</v>
+        <v>19330051920092</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5733,22 +5616,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920084</v>
+        <v>19330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5756,16 +5639,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920090</v>
+        <v>19330051920097</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5779,16 +5662,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920090</v>
+        <v>19330051920097</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5802,16 +5685,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920089</v>
+        <v>19330051920100</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5825,16 +5708,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920089</v>
+        <v>19330051920100</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5848,16 +5731,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920097</v>
+        <v>19330051920102</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5871,16 +5754,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920097</v>
+        <v>19330051920102</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5894,16 +5777,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920100</v>
+        <v>19330051920106</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5917,16 +5800,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920100</v>
+        <v>19330051920106</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5940,16 +5823,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920102</v>
+        <v>19330051920109</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5963,16 +5846,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920102</v>
+        <v>19330051920109</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5986,16 +5869,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920106</v>
+        <v>19330051920110</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6009,16 +5892,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920106</v>
+        <v>19330051920110</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6032,16 +5915,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920107</v>
+        <v>19330051920001</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -6055,16 +5938,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920107</v>
+        <v>19330051920001</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6078,16 +5961,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920109</v>
+        <v>19330051920116</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -6101,16 +5984,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920109</v>
+        <v>19330051920116</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6124,16 +6007,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920110</v>
+        <v>19330051920117</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -6147,16 +6030,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920110</v>
+        <v>19330051920117</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6170,16 +6053,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920001</v>
+        <v>19330051920118</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -6193,16 +6076,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920001</v>
+        <v>19330051920118</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6216,16 +6099,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920116</v>
+        <v>19330051920119</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -6239,16 +6122,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920116</v>
+        <v>19330051920119</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -6262,16 +6145,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920117</v>
+        <v>19330051920120</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -6285,16 +6168,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920117</v>
+        <v>19330051920120</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -6308,16 +6191,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920118</v>
+        <v>19330051920122</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -6331,16 +6214,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920118</v>
+        <v>19330051920122</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -6354,16 +6237,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920119</v>
+        <v>19330051920084</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -6377,22 +6260,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920119</v>
+        <v>19330051920090</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -6400,16 +6283,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920120</v>
+        <v>19330051920089</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -6423,22 +6306,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920120</v>
+        <v>19330051920107</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G35">
         <v>-1</v>
@@ -6464,75 +6347,6 @@
         <v>52</v>
       </c>
       <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>19330051920121</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>19330051920122</v>
-      </c>
-      <c r="B38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>19330051920122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -206,48 +206,165 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CONDADO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CONDADO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>JUAN</t>
   </si>
   <si>
@@ -257,33 +374,9 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>TOCOHUA</t>
   </si>
   <si>
@@ -293,51 +386,15 @@
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
@@ -347,57 +404,15 @@
     <t>JOSE JAZAEL</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
     <t>BRAYAN</t>
   </si>
   <si>
     <t>BRANDON</t>
   </si>
   <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>OSWALDO ENRIQUE</t>
   </si>
   <si>
@@ -407,22 +422,7 @@
     <t>YAEL</t>
   </si>
   <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
     <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
   </si>
   <si>
     <t>JOSUE GILBERTO</t>
@@ -917,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -971,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -994,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1006,7 +1006,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1048,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1060,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1148,7 +1148,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1202,7 +1202,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1225,7 +1225,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1522,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1610,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1776,7 +1776,7 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1830,7 +1830,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1841,7 +1841,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1895,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1918,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1930,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1972,7 +1972,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -1984,7 +1984,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1995,7 +1995,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2049,7 +2049,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2161,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2226,7 +2226,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2303,7 +2303,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2380,7 +2380,7 @@
         <v>7</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -2392,7 +2392,7 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2434,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2446,7 +2446,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2457,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2511,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2523,7 +2523,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2546,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2600,7 +2600,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2611,7 +2611,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2623,7 +2623,7 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2665,7 +2665,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2677,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2688,7 +2688,7 @@
         <v>-1</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2700,7 +2700,7 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2742,7 +2742,7 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2754,7 +2754,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2777,7 +2777,7 @@
         <v>7</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3008,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3062,7 +3062,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3085,7 +3085,7 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3139,7 +3139,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3239,7 +3239,7 @@
         <v>7</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3281,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3293,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3358,22 +3358,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.5</v>
+      </c>
       <c r="I2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3387,25 +3390,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3543,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3572,16 +3575,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>19330051920088</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3592,16 +3595,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920085</v>
+        <v>19330051920088</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3612,36 +3615,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920084</v>
+        <v>19330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920088</v>
+        <v>19330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3652,136 +3655,136 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920088</v>
+        <v>19330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920088</v>
+        <v>19330051920093</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920090</v>
+        <v>19330051920093</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920089</v>
+        <v>19330051920093</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -3792,16 +3795,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -3812,376 +3815,376 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920094</v>
+        <v>19330051920095</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920094</v>
+        <v>19330051920097</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920095</v>
+        <v>19330051920099</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920095</v>
+        <v>19330051920099</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920095</v>
+        <v>19330051920100</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920097</v>
+        <v>19330051920101</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920097</v>
+        <v>19330051920105</v>
       </c>
       <c r="B25" t="s">
         <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920098</v>
+        <v>19330051920105</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920098</v>
+        <v>19330051920103</v>
       </c>
       <c r="B27" t="s">
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920098</v>
+        <v>19330051920103</v>
       </c>
       <c r="B28" t="s">
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920099</v>
+        <v>19330051920106</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920099</v>
+        <v>19330051920112</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920099</v>
+        <v>19330051920115</v>
       </c>
       <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
         <v>71</v>
       </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920100</v>
+        <v>19330051920116</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -4192,96 +4195,96 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920100</v>
+        <v>19330051920117</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920101</v>
+        <v>19330051920117</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920101</v>
+        <v>19330051920118</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920101</v>
+        <v>19330051920118</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920102</v>
+        <v>19330051920119</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
@@ -4292,662 +4295,22 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920102</v>
+        <v>19330051920120</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920105</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920105</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920105</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920103</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920103</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920106</v>
-      </c>
-      <c r="B44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920106</v>
-      </c>
-      <c r="B45" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920107</v>
-      </c>
-      <c r="B46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920109</v>
-      </c>
-      <c r="B47" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920109</v>
-      </c>
-      <c r="B48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920110</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" t="s">
-        <v>128</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920110</v>
-      </c>
-      <c r="B50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920112</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" t="s">
-        <v>69</v>
-      </c>
-      <c r="D52" t="s">
-        <v>129</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920001</v>
-      </c>
-      <c r="B53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920001</v>
-      </c>
-      <c r="B54" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" t="s">
-        <v>130</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920115</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" t="s">
-        <v>109</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920115</v>
-      </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" t="s">
-        <v>74</v>
-      </c>
-      <c r="D56" t="s">
-        <v>109</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920115</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" t="s">
-        <v>74</v>
-      </c>
-      <c r="D57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920116</v>
-      </c>
-      <c r="B58" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" t="s">
-        <v>115</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920116</v>
-      </c>
-      <c r="B59" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920117</v>
-      </c>
-      <c r="B60" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" t="s">
-        <v>131</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920117</v>
-      </c>
-      <c r="B61" t="s">
-        <v>83</v>
-      </c>
-      <c r="C61" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" t="s">
-        <v>131</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920118</v>
-      </c>
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" t="s">
-        <v>132</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920118</v>
-      </c>
-      <c r="B63" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" t="s">
-        <v>132</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920119</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" t="s">
-        <v>133</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920119</v>
-      </c>
-      <c r="B65" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" t="s">
-        <v>133</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920120</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920120</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" t="s">
-        <v>134</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920121</v>
-      </c>
-      <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" t="s">
-        <v>106</v>
-      </c>
-      <c r="D68" t="s">
-        <v>135</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920122</v>
-      </c>
-      <c r="B69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920122</v>
-      </c>
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4986,13 +4349,13 @@
         <v>19330051920093</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -5003,13 +4366,13 @@
         <v>19330051920095</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5020,13 +4383,13 @@
         <v>19330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5034,70 +4397,70 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920094</v>
+        <v>19330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920098</v>
+        <v>19330051920094</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920099</v>
+        <v>19330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920101</v>
+        <v>19330051920099</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5105,44 +4468,44 @@
         <v>19330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920115</v>
+        <v>19330051920103</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920085</v>
+        <v>19330051920117</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>108</v>
@@ -5153,16 +4516,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920092</v>
+        <v>19330051920118</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5173,16 +4536,16 @@
         <v>19330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5190,322 +4553,322 @@
         <v>19330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920102</v>
+        <v>19330051920101</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920103</v>
+        <v>19330051920106</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920106</v>
+        <v>19330051920112</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920109</v>
+        <v>19330051920115</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920110</v>
+        <v>19330051920116</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920112</v>
+        <v>19330051920119</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920001</v>
+        <v>19330051920120</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920116</v>
+        <v>19330051920085</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920117</v>
+        <v>19330051920084</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920118</v>
+        <v>19330051920090</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920119</v>
+        <v>19330051920089</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920120</v>
+        <v>19330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920122</v>
+        <v>19330051920107</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920084</v>
+        <v>19330051920109</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920090</v>
+        <v>19330051920110</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920089</v>
+        <v>19330051920001</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920107</v>
+        <v>19330051920121</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920121</v>
+        <v>19330051920122</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5515,7 +4878,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5547,16 +4910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5570,22 +4933,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5593,22 +4956,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5616,22 +4979,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5639,22 +5002,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920097</v>
+        <v>19330051920101</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5662,45 +5025,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920097</v>
+        <v>19330051920101</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920100</v>
+        <v>19330051920105</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5708,22 +5071,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920100</v>
+        <v>19330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5731,16 +5094,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920102</v>
+        <v>19330051920112</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5754,39 +5117,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920102</v>
+        <v>19330051920112</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920106</v>
+        <v>19330051920117</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5800,16 +5163,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920106</v>
+        <v>19330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5823,7 +5186,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920109</v>
+        <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
         <v>77</v>
@@ -5832,7 +5195,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5846,7 +5209,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920109</v>
+        <v>19330051920118</v>
       </c>
       <c r="B15" t="s">
         <v>77</v>
@@ -5855,7 +5218,7 @@
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5869,22 +5232,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920110</v>
+        <v>19330051920097</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -5892,16 +5255,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920110</v>
+        <v>19330051920100</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
         <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5915,22 +5278,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920001</v>
+        <v>19330051920106</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -5938,22 +5301,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920001</v>
+        <v>19330051920115</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -5964,13 +5327,13 @@
         <v>19330051920116</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -5984,22 +5347,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920116</v>
+        <v>19330051920119</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6007,16 +5370,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920117</v>
+        <v>19330051920120</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -6025,328 +5388,6 @@
         <v>52</v>
       </c>
       <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920117</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920118</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920118</v>
-      </c>
-      <c r="B25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920119</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920119</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920120</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920120</v>
-      </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920122</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920122</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920084</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330051920090</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>19330051920089</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>19330051920107</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>19330051920121</v>
-      </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -221,196 +221,196 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>FLORENCIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>OCTAVIANO</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GARATE</t>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
   </si>
   <si>
     <t>BERNABE</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>ANTEMATE</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>MIRON</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JAFET</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
   </si>
   <si>
     <t>JESUS ENRIQUE</t>
   </si>
   <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
     <t>JUAN LUIS</t>
   </si>
   <si>
     <t>AXEL MIGUEL</t>
   </si>
   <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
+    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>OSWALDO ENRIQUE</t>
@@ -932,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -941,13 +941,13 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -968,7 +968,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1009,7 +1009,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1018,13 +1018,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1060,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1083,10 +1083,10 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1095,13 +1095,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1122,7 +1122,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1172,13 +1172,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1240,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1249,13 +1249,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1317,7 +1317,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1326,13 +1326,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1353,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1376,7 +1376,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1385,16 +1385,16 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1403,13 +1403,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1430,7 +1430,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1439,13 +1439,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1453,7 +1453,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>-1</v>
@@ -1471,7 +1471,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1480,13 +1480,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1507,7 +1507,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1516,13 +1516,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1530,7 +1530,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>-1</v>
@@ -1545,10 +1545,10 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1557,13 +1557,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1584,7 +1584,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1593,13 +1593,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1622,10 +1622,10 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1634,13 +1634,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1676,7 +1676,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1702,7 +1702,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1711,13 +1711,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1770,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1788,13 +1788,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1865,13 +1865,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1924,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1933,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1942,13 +1942,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1978,13 +1978,13 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2010,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2019,13 +2019,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2084,10 +2084,10 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2096,13 +2096,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2138,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2146,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>-1</v>
@@ -2164,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2173,13 +2173,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2209,13 +2209,13 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2238,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2250,13 +2250,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2292,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2318,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2327,13 +2327,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2363,13 +2363,13 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2395,7 +2395,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2404,13 +2404,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2481,13 +2481,13 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2523,7 +2523,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2549,7 +2549,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2558,13 +2558,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2585,7 +2585,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2594,13 +2594,13 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2626,7 +2626,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2635,13 +2635,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2662,7 +2662,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2677,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2685,7 +2685,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -2703,7 +2703,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2712,13 +2712,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2739,7 +2739,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2780,7 +2780,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2789,13 +2789,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2816,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2825,13 +2825,13 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2854,10 +2854,10 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2866,13 +2866,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2893,7 +2893,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -2902,13 +2902,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2931,10 +2931,10 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2943,13 +2943,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2985,7 +2985,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3011,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3020,13 +3020,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3062,7 +3062,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3088,7 +3088,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3097,13 +3097,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3139,7 +3139,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3165,7 +3165,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3174,13 +3174,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3242,7 +3242,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3251,13 +3251,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3278,7 +3278,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3293,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3390,25 +3390,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E3">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>51.61</v>
+      </c>
+      <c r="G3">
+        <v>48.39</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>70.97</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>6.3</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>29.03</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3454,25 +3454,25 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="G5">
+        <v>19.35</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>83.87</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>6.8</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>16.13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3518,25 +3518,25 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3581,10 +3581,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3601,36 +3601,36 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920088</v>
+        <v>19330051920092</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3641,36 +3641,36 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3681,70 +3681,70 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -3755,76 +3755,76 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920093</v>
+        <v>19330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920094</v>
+        <v>19330051920099</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920095</v>
+        <v>19330051920105</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -3835,96 +3835,96 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920095</v>
+        <v>19330051920103</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920095</v>
+        <v>19330051920112</v>
       </c>
       <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
         <v>66</v>
       </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920095</v>
+        <v>19330051920116</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920097</v>
+        <v>19330051920117</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920098</v>
+        <v>19330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -3935,381 +3935,41 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920098</v>
+        <v>19330051920119</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920099</v>
+        <v>19330051920120</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
         <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920099</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920100</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920101</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920105</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920105</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920103</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920103</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920106</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920112</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920116</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920117</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920117</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920118</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920118</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920119</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4346,67 +4006,67 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920093</v>
+        <v>19330051920088</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920095</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920088</v>
+        <v>19330051920093</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4414,16 +4074,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4431,19 +4091,19 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920098</v>
+        <v>19330051920094</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4451,16 +4111,16 @@
         <v>19330051920099</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4468,16 +4128,16 @@
         <v>19330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4485,64 +4145,64 @@
         <v>19330051920103</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920117</v>
+        <v>19330051920112</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920118</v>
+        <v>19330051920116</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920097</v>
+        <v>19330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4550,16 +4210,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920100</v>
+        <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4567,16 +4227,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920101</v>
+        <v>19330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4584,16 +4244,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920106</v>
+        <v>19330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4601,98 +4261,98 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920112</v>
+        <v>19330051920085</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920115</v>
+        <v>19330051920084</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920116</v>
+        <v>19330051920090</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920119</v>
+        <v>19330051920089</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920120</v>
+        <v>19330051920097</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920085</v>
+        <v>19330051920100</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
@@ -4703,16 +4363,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920084</v>
+        <v>19330051920101</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4720,16 +4380,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920090</v>
+        <v>19330051920102</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4737,16 +4397,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920089</v>
+        <v>19330051920106</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4754,16 +4414,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920102</v>
+        <v>19330051920107</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4771,16 +4431,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920107</v>
+        <v>19330051920109</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4788,16 +4448,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920109</v>
+        <v>19330051920110</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4805,16 +4465,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920110</v>
+        <v>19330051920001</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4822,16 +4482,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920001</v>
+        <v>19330051920115</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4842,10 +4502,10 @@
         <v>19330051920121</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>135</v>
@@ -4859,10 +4519,10 @@
         <v>19330051920122</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -4878,7 +4538,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4910,16 +4570,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4933,91 +4593,91 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920094</v>
+        <v>19330051920101</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920094</v>
+        <v>19330051920101</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920101</v>
+        <v>19330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5025,22 +4685,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920101</v>
+        <v>19330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5048,22 +4708,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920105</v>
+        <v>19330051920103</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5071,68 +4731,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920105</v>
+        <v>19330051920103</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920112</v>
+        <v>19330051920001</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920112</v>
+        <v>19330051920001</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5140,16 +4800,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920117</v>
+        <v>19330051920118</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5163,16 +4823,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920117</v>
+        <v>19330051920118</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5181,21 +4841,21 @@
         <v>53</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5209,16 +4869,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5227,27 +4887,27 @@
         <v>53</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920097</v>
+        <v>19330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
         <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -5255,16 +4915,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920100</v>
+        <v>19330051920120</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5273,21 +4933,21 @@
         <v>53</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920106</v>
+        <v>19330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -5296,67 +4956,67 @@
         <v>53</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920115</v>
+        <v>19330051920102</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920116</v>
+        <v>19330051920110</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920119</v>
+        <v>19330051920116</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -5370,16 +5030,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920120</v>
+        <v>19330051920117</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -5389,6 +5049,29 @@
       </c>
       <c r="G22">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -176,12 +176,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
@@ -206,22 +206,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CONDADO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>CADEZA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>CONDADO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERRERA</t>
@@ -230,7 +257,22 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
   </si>
   <si>
     <t>ROJAS</t>
@@ -248,24 +290,54 @@
     <t>TAPIA</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>GARATE</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>AVELINO</t>
   </si>
   <si>
     <t>DEL ANGEL</t>
   </si>
   <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
@@ -275,36 +347,72 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
     <t>IRVING OTTONIEL</t>
   </si>
   <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
     <t>ELEAZAR RIGOBERTO</t>
   </si>
   <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
+    <t>JESUS ENRIQUE</t>
   </si>
   <si>
     <t>ADRIANA</t>
   </si>
   <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>AXEL</t>
   </si>
   <si>
     <t>URIEL</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>OSWALDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>JOSE ALONSO</t>
   </si>
   <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
     <t>YARITZI</t>
   </si>
   <si>
@@ -315,114 +423,6 @@
   </si>
   <si>
     <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>OSWALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
   </si>
   <si>
     <t>JOSUE GILBERTO</t>
@@ -935,16 +935,16 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -971,16 +971,16 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1012,16 +1012,16 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1051,13 +1051,13 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1071,10 +1071,10 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1089,16 +1089,16 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1125,16 +1125,16 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1166,7 +1166,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1175,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1243,7 +1243,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1252,7 +1252,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1288,7 +1288,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1302,10 +1302,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1356,16 +1356,16 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1406,7 +1406,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1442,7 +1442,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1456,7 +1456,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -1483,7 +1483,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1510,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1533,7 +1533,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1560,7 +1560,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1628,7 +1628,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1637,7 +1637,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1687,7 +1687,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1714,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1741,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1764,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1791,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1859,16 +1859,16 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1945,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2013,7 +2013,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2022,7 +2022,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2058,7 +2058,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2072,7 +2072,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2090,7 +2090,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2099,7 +2099,7 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2126,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2170,13 +2170,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2203,16 +2203,16 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2253,7 +2253,7 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2321,16 +2321,16 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2366,7 +2366,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2398,16 +2398,16 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2434,16 +2434,16 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2475,16 +2475,16 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2511,16 +2511,16 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2534,7 +2534,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2561,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -2588,7 +2588,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2629,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2638,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2706,7 +2706,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2715,7 +2715,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -2751,7 +2751,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2765,7 +2765,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -2783,16 +2783,16 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -2819,16 +2819,16 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2842,7 +2842,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -2860,16 +2860,16 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -2896,7 +2896,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2905,7 +2905,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2919,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -2940,13 +2940,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -2973,10 +2973,10 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -2996,7 +2996,7 @@
         <v>7</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3023,7 +3023,7 @@
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -3050,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3059,7 +3059,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3073,7 +3073,7 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -3091,16 +3091,16 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -3127,16 +3127,16 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3168,7 +3168,7 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3177,7 +3177,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>6</v>
@@ -3245,7 +3245,7 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3254,7 +3254,7 @@
         <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3290,7 +3290,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -3361,27 +3361,27 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>51.61</v>
       </c>
       <c r="G2">
+        <v>48.39</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>8.5</v>
-      </c>
-      <c r="I2">
-        <v>15</v>
-      </c>
       <c r="J2">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3390,19 +3390,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="G3">
-        <v>48.39</v>
+        <v>32.26</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3422,19 +3422,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G4">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3486,25 +3486,25 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3546,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3575,36 +3575,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920088</v>
+        <v>19330051920093</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920088</v>
+        <v>19330051920095</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -3615,362 +3615,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920092</v>
+        <v>19330051920098</v>
       </c>
       <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
         <v>63</v>
       </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920092</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920093</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920093</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920094</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920095</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920095</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920098</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920098</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920099</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920105</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920103</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920116</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920117</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920118</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920119</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920120</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -4006,271 +3666,271 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920088</v>
+        <v>19330051920093</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920092</v>
+        <v>19330051920095</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920093</v>
+        <v>19330051920098</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920095</v>
+        <v>19330051920085</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920098</v>
+        <v>19330051920084</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920094</v>
+        <v>19330051920088</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920099</v>
+        <v>19330051920090</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920105</v>
+        <v>19330051920089</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920103</v>
+        <v>19330051920092</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920112</v>
+        <v>19330051920094</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920116</v>
+        <v>19330051920097</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920117</v>
+        <v>19330051920099</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920118</v>
+        <v>19330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920119</v>
+        <v>19330051920101</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920120</v>
+        <v>19330051920102</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920085</v>
+        <v>19330051920105</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4278,16 +3938,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920084</v>
+        <v>19330051920103</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4295,16 +3955,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920090</v>
+        <v>19330051920106</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4312,16 +3972,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920089</v>
+        <v>19330051920107</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4329,16 +3989,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920097</v>
+        <v>19330051920109</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4346,16 +4006,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920100</v>
+        <v>19330051920110</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4363,16 +4023,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920101</v>
+        <v>19330051920112</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4380,16 +4040,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920102</v>
+        <v>19330051920001</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4397,16 +4057,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920106</v>
+        <v>19330051920115</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4414,16 +4074,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920107</v>
+        <v>19330051920116</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4431,16 +4091,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920109</v>
+        <v>19330051920117</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4448,16 +4108,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920110</v>
+        <v>19330051920118</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4465,16 +4125,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920001</v>
+        <v>19330051920119</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4482,16 +4142,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920115</v>
+        <v>19330051920120</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4502,10 +4162,10 @@
         <v>19330051920121</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
         <v>135</v>
@@ -4519,10 +4179,10 @@
         <v>19330051920122</v>
       </c>
       <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
         <v>110</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -4538,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4573,22 +4233,22 @@
         <v>19330051920094</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4596,19 +4256,19 @@
         <v>19330051920094</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4619,13 +4279,13 @@
         <v>19330051920101</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -4642,19 +4302,19 @@
         <v>19330051920101</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4665,22 +4325,22 @@
         <v>19330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4688,19 +4348,19 @@
         <v>19330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4708,45 +4368,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920103</v>
+        <v>19330051920001</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920103</v>
+        <v>19330051920001</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4754,22 +4414,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920001</v>
+        <v>19330051920118</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4777,22 +4437,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920001</v>
+        <v>19330051920118</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4800,45 +4460,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4846,45 +4506,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920119</v>
+        <v>19330051920085</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>52</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920119</v>
+        <v>19330051920088</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4892,45 +4552,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920120</v>
+        <v>19330051920102</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920120</v>
+        <v>19330051920110</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -4938,22 +4598,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920085</v>
+        <v>19330051920120</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -4961,116 +4621,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920102</v>
+        <v>19330051920122</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920116</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920117</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920122</v>
-      </c>
-      <c r="B23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1246,7 +1246,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1477,7 +1477,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>7</v>
@@ -1513,7 +1513,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1631,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1939,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -1975,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2016,7 +2016,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -2129,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2247,7 +2247,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -2555,7 +2555,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2632,7 +2632,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -2745,7 +2745,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -3017,7 +3017,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -3171,7 +3171,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>9</v>
@@ -3284,7 +3284,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>3</v>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -206,175 +206,175 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>CONDADO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
     <t>JOSUE ALEXIS</t>
   </si>
   <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
     <t>JAFET</t>
   </si>
   <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
     <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
   </si>
   <si>
     <t>ADRIANA</t>
@@ -950,19 +950,19 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -974,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1027,19 +1027,19 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1104,31 +1104,31 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>8</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1181,19 +1181,19 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1258,19 +1258,19 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1282,13 +1282,13 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1320,10 +1320,10 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -1335,37 +1335,37 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1382,7 +1382,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1397,10 +1397,10 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1412,37 +1412,37 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1474,7 +1474,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1489,19 +1489,19 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1510,16 +1510,16 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1536,7 +1536,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -1551,10 +1551,10 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1566,37 +1566,37 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1643,19 +1643,19 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1664,16 +1664,16 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1690,7 +1690,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -1705,10 +1705,10 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -1720,37 +1720,37 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1782,7 +1782,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -1797,19 +1797,19 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1818,16 +1818,16 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1874,25 +1874,25 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1951,19 +1951,19 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2028,28 +2028,28 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2058,7 +2058,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2105,19 +2105,19 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2126,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2167,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -2182,19 +2182,19 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2203,16 +2203,16 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2259,19 +2259,19 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2283,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2336,19 +2336,19 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2357,10 +2357,10 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2413,19 +2413,19 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2434,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2490,19 +2490,19 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2520,7 +2520,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2552,7 +2552,7 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2567,28 +2567,28 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2597,7 +2597,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2644,25 +2644,25 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2671,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2721,19 +2721,19 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2798,19 +2798,19 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2822,13 +2822,13 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2875,28 +2875,28 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2905,7 +2905,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2937,7 +2937,7 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -2952,19 +2952,19 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2973,10 +2973,10 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3014,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -3029,28 +3029,28 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3106,19 +3106,19 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3127,7 +3127,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3183,31 +3183,31 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>10</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3260,19 +3260,19 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3390,19 +3390,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>67.73999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="G3">
-        <v>32.26</v>
+        <v>3.23</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3422,19 +3422,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3454,19 +3454,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3486,25 +3486,25 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3546,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3571,66 +3571,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920093</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920095</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920098</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3666,64 +3606,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920093</v>
+        <v>19330051920085</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920095</v>
+        <v>19330051920084</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920098</v>
+        <v>19330051920088</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920085</v>
+        <v>19330051920090</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
         <v>111</v>
@@ -3734,13 +3674,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920084</v>
+        <v>19330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -3751,13 +3691,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920088</v>
+        <v>19330051920092</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>113</v>
@@ -3768,13 +3708,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920090</v>
+        <v>19330051920093</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
         <v>114</v>
@@ -3785,13 +3725,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920089</v>
+        <v>19330051920094</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
         <v>115</v>
@@ -3802,13 +3742,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920092</v>
+        <v>19330051920095</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>116</v>
@@ -3819,13 +3759,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920094</v>
+        <v>19330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
@@ -3836,13 +3776,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920097</v>
+        <v>19330051920098</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>118</v>
@@ -3856,10 +3796,10 @@
         <v>19330051920099</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
@@ -3873,10 +3813,10 @@
         <v>19330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>120</v>
@@ -3890,10 +3830,10 @@
         <v>19330051920101</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>121</v>
@@ -3907,10 +3847,10 @@
         <v>19330051920102</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>122</v>
@@ -3924,10 +3864,10 @@
         <v>19330051920105</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>123</v>
@@ -3941,10 +3881,10 @@
         <v>19330051920103</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>124</v>
@@ -3958,10 +3898,10 @@
         <v>19330051920106</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>125</v>
@@ -3975,10 +3915,10 @@
         <v>19330051920107</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
         <v>126</v>
@@ -3992,10 +3932,10 @@
         <v>19330051920109</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
         <v>127</v>
@@ -4009,10 +3949,10 @@
         <v>19330051920110</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
         <v>128</v>
@@ -4026,10 +3966,10 @@
         <v>19330051920112</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
         <v>129</v>
@@ -4043,10 +3983,10 @@
         <v>19330051920001</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
         <v>130</v>
@@ -4060,13 +4000,13 @@
         <v>19330051920115</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4077,13 +4017,13 @@
         <v>19330051920116</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4094,10 +4034,10 @@
         <v>19330051920117</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
         <v>131</v>
@@ -4111,10 +4051,10 @@
         <v>19330051920118</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
         <v>132</v>
@@ -4128,10 +4068,10 @@
         <v>19330051920119</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>133</v>
@@ -4145,10 +4085,10 @@
         <v>19330051920120</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>134</v>
@@ -4162,10 +4102,10 @@
         <v>19330051920121</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>135</v>
@@ -4179,10 +4119,10 @@
         <v>19330051920122</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -4198,7 +4138,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4230,19 +4170,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -4253,16 +4193,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4276,22 +4216,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920101</v>
+        <v>19330051920085</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4299,16 +4239,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920101</v>
+        <v>19330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4322,22 +4262,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920105</v>
+        <v>19330051920095</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4345,16 +4285,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920105</v>
+        <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4368,22 +4308,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920001</v>
+        <v>19330051920101</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4391,16 +4331,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920001</v>
+        <v>19330051920102</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4414,22 +4354,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920118</v>
+        <v>19330051920105</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4437,16 +4377,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920118</v>
+        <v>19330051920110</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4460,22 +4400,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920119</v>
+        <v>19330051920112</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4483,16 +4423,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920119</v>
+        <v>19330051920001</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4506,16 +4446,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920085</v>
+        <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4529,22 +4469,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920088</v>
+        <v>19330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4552,16 +4492,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920102</v>
+        <v>19330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -4575,16 +4515,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920110</v>
+        <v>19330051920122</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4593,52 +4533,6 @@
         <v>52</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920120</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920122</v>
-      </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20212.xlsx
+++ b/grupos/6BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -176,19 +176,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -983,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1042,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1119,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1137,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1196,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1273,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1350,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1427,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1504,7 +1504,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1522,7 +1522,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1581,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1599,7 +1599,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1658,7 +1658,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1676,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1735,7 +1735,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1812,7 +1812,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1830,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1889,7 +1889,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1966,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -1984,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2043,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2120,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2197,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2274,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2351,7 +2351,7 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2428,7 +2428,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2505,7 +2505,7 @@
         <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2523,7 +2523,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2582,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2600,7 +2600,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2659,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2677,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2736,7 +2736,7 @@
         <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2813,7 +2813,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2890,7 +2890,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2908,7 +2908,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -2985,7 +2985,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3062,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3121,7 +3121,7 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3139,7 +3139,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3198,7 +3198,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3275,7 +3275,7 @@
         <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3293,7 +3293,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -3358,19 +3358,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>51.61</v>
+        <v>96.77</v>
       </c>
       <c r="G2">
-        <v>48.39</v>
+        <v>3.23</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3390,16 +3390,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4138,7 +4138,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4185,354 +4185,9 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920098</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920085</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920094</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920095</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920099</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920001</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920118</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920119</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920120</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920122</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>
